--- a/www/download/COUNTRY.ROU.WIOD16.xlsx
+++ b/www/download/COUNTRY.ROU.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>Romênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2.14429026656224</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2.89623970153542</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>3.30540204541294</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>3.31956041574456</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>3.25713469838084</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>2.90992480700026</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>2.80569804920364</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>2.43396978430916</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>2.49916529503634</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>3.0414266887548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>3.16973664006928</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>3.04208046284928</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>3.46362842534526</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>3.3272094749872</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>3.34425431100004</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>10.706</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10.63</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>9.568</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>9.569</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>9.411</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9.266</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>9.319</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>9.366</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>9.349</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>9.186</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>9.134</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>9.073</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>8.628</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>8.569</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>8.804</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>5.846</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5.772</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>6.134</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>6.408</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>6.162</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>6.404</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>6.437</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>6.501</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>6.245</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>6.012</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>6.133</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>5.895</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>5.897</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>6.171</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>20661.817</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20587.813</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>18217.555</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>18612.148</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>18234.078</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>17993.604</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>17880.91</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>18146.449</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>17925.126</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>17592.821</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>17407.229</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>17693.624</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>14453.559</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>14325.894</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>14814.339</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11408.567</t>
+          <t>33634468070.3527</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11290.436</t>
+          <t>32783832232.1269</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11921.931</t>
+          <t>27375152975.7614</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11554.795</t>
+          <t>27903946959.1981</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12478.508</t>
+          <t>26403251745.2372</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11990.175</t>
+          <t>26140900157.9718</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12362.531</t>
+          <t>25238234376.831</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>12500.772</t>
+          <t>25828401210.2654</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>12607.212</t>
+          <t>25288666304.6498</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>24527780722.4604</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>11459.093</t>
+          <t>23152668007.2258</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>12042.35</t>
+          <t>23498042369.122</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>11191.338</t>
+          <t>18121406119.2553</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>11156.219</t>
+          <t>18063044043.7328</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>11688.135</t>
+          <t>18184664895.9023</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7162799723.85714</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7144102043.52001</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5637990283.68396</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5804778679.87063</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5264454114.43731</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6006781034.59423</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6062782646.24209</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6156470394.2109</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6406432023.14219</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5780968526.2417</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5339354054.29117</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4887023169.45075</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3600171327.08127</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3409828644.83589</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3710947187.34471</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>15088161.6714897</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>13279575.3748007</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11153463.481263</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>8681625.85546787</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6594582.57072223</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5386559.70722659</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4283178.68184254</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3335201.83895563</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2678033.0415828</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2963741.243761</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2663465.92729351</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2435711.92378612</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2318542.46255531</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2048262.9367316</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2060462.94382599</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>133652.171903351</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>131592.894273128</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>112222.330350992</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>125902.062967545</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>132402.122481561</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>141060.584945447</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>145296.972778647</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>164787.508305253</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>176547.439601239</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>154365.70462062</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>171885.917074101</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>182406.640622327</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>133807.08914686</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>132133.676611107</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>132837.000484056</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>273292.368853789</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>263876.859230536</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>221664.930264897</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>245897.105677109</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>257238.026891644</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>273446.390547135</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>278903.082468789</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>322263.420056239</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>342475.315007184</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>302287.1140086</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>316122.863966993</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>340719.80660482</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>256019.240977592</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>254941.051650042</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>257846.534212679</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.592752476660974</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.580385600768522</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.11457104395895</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.99056598661872</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.37033275031855</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.996106555399011</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1.03908530477547</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1.03050956141279</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.967899129259236</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.0833879211292</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.14615717247491</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.46414833375006</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.10855706110883</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.2717828847194</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.14963657792263</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10709.7814480995</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11867.2069581224</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>13144.3735824057</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>16476.6458456056</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>19951.3956042949</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>25599.7102282455</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>30526.7670475514</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>43141.4790229041</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>51478.4927585944</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>43890.3736316759</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>46701.5730756354</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>55369.1182903681</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>53433.5558177998</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>60924.4951219508</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>62627.4792474356</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.14429026656224</t>
+          <t>1225.16415637951</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.89623970153542</t>
+          <t>1237.80269656941</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.30540204541294</t>
+          <t>919.077706651663</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.31956041574456</t>
+          <t>983.844117874381</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.25713469838084</t>
+          <t>821.595310949077</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.90992480700026</t>
+          <t>974.873577414021</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.80569804920364</t>
+          <t>946.732873130762</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.43396978430916</t>
+          <t>956.41920059203</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.49916529503634</t>
+          <t>985.438160179384</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.0414266887548</t>
+          <t>925.739991711643</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3.16973664006928</t>
+          <t>888.071795201697</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>3.04208046284928</t>
+          <t>796.866548632069</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3.46362842534526</t>
+          <t>610.716086018875</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>3.3272094749872</t>
+          <t>578.191854857376</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3.34425431100004</t>
+          <t>601.381883310599</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-2491765193.4683</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-2602873393.04199</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-2360954456.05106</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>-2322098194.63164</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-1945520466.64035</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>-1595252656.19744</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>-866517136.137789</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-1205068548.3432</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>-1224713951.65096</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-728372184.068499</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-869317151.783748</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>-858356566.524774</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>-331694413.436296</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>117905625.81984</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>490582641.041838</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-2637700871.72641</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-2734084706.47443</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-2526512949.25413</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-2509709393.05399</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-2128882817.63108</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>-1811105575.80678</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>-1222897600.15526</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-1616008851.86269</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-1626049834.48986</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1194443782.47694</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-1133369259.56401</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>-1179522985.54682</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-803888810.435355</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>-615318820.706868</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>-468793576.818684</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>145935678.258107</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>131211313.432444</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>165558493.203076</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>187611198.422348</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>183362350.990724</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>215852919.609343</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>356380464.017468</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>410940303.519494</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>401335882.838901</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>466071598.408443</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>264052107.780257</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>321166419.022049</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>472194396.999058</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>733224446.526707</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>959376217.860522</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>1951.38324438971</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1956.20555825075</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1943.4551056338</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>1958.40663717564</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1947.45427305075</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1945.95153856141</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>1930.4690891488</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>1942.01833152089</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>1939.24289735583</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1928.67551683828</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>1905.9416529448</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1963.59737803287</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>1898.44580152672</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>1891.71821480652</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>1894.13437697506</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>1929.83861910695</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>1936.71044401372</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1903.9290405806</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1945.02600668556</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1937.54875584173</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1941.87462254125</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>1918.65548135312</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>1937.46053561301</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>1917.37185896031</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1915.26090453376</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1905.72016118171</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>1950.14044525024</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1675.23110599929</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>1671.76941985192</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>1682.70190654604</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>11535.4375852489</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12506.2565781688</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>15072.1911485246</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>18911.0312454521</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>24889.545366191</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>30034.2336771048</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>36537.5862309898</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>46333.0589106935</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>52221.8770614533</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>43351.2592270769</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>50809.9499248717</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>63888.450250591</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>60740.1790650863</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>71728.0430082567</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>77647.7377211243</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3978439858.1322</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4060904506.0556</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>4129538101.97948</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>4089675871.08706</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>4047859110.68765</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3589225331.70466</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3482506457.49322</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>3155883328.73623</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3058289551.12412</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2986753654.23113</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>3367038486.34406</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3958066522.28033</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>3199566650.96194</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>3489595302.00515</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>3564931588.50999</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>13037.7344912163</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15023.903065801</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>17024.5810692313</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>22682.5147482084</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>30822.6171736254</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>39108.9677061105</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>49665.0019714241</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>67367.8243162983</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>76149.2987757016</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>51849.1014607773</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>59188.6191942133</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>72692.4269908154</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>68029.6682689912</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>72305.2914479322</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>77279.7200960812</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>20661.817</t>
+          <t>1718780961.39967</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20587.813</t>
+          <t>1861080859.98642</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18217.555</t>
+          <t>2083846911.01549</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>18612.148</t>
+          <t>2341396008.84473</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>18234.078</t>
+          <t>2921072806.82278</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17993.604</t>
+          <t>3138224663.50321</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>17880.91</t>
+          <t>4122582838.19879</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>18146.449</t>
+          <t>4008029584.90364</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>17925.126</t>
+          <t>3893522844.64445</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>17592.821</t>
+          <t>3085645055.8638</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>17407.229</t>
+          <t>3222331938.41833</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17693.624</t>
+          <t>3822070291.61953</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>14453.559</t>
+          <t>3472382660.43132</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>14325.894</t>
+          <t>3655637734.93203</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>14814.339</t>
+          <t>4025124781.52244</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11408.567</t>
+          <t>-1502.29690596733</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11290.436</t>
+          <t>-2517.64648763217</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11921.931</t>
+          <t>-1952.38992070672</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11554.795</t>
+          <t>-3771.48350275628</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12478.508</t>
+          <t>-5933.07180743442</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>11990.175</t>
+          <t>-9074.73402900573</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>12362.531</t>
+          <t>-13127.4157404344</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>12500.772</t>
+          <t>-21034.7654056048</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>12607.212</t>
+          <t>-23927.4217142483</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>-8497.84223370034</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>11459.093</t>
+          <t>-8378.66926934156</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>12042.35</t>
+          <t>-8803.97674022447</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>11191.338</t>
+          <t>-7289.48920390484</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>11156.219</t>
+          <t>-577.248439675537</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>11688.135</t>
+          <t>368.017625043058</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>33634.822</t>
+          <t>2259658896.73253</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>32784.755</t>
+          <t>2199823646.06918</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>27376.326</t>
+          <t>2045691190.96399</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>27904.437</t>
+          <t>1748279862.24233</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>26403.587</t>
+          <t>1126786303.86488</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>26141.405</t>
+          <t>451000668.201444</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>25240.109</t>
+          <t>-640076380.705576</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>25830.541</t>
+          <t>-852146256.167411</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>25287.108</t>
+          <t>-835233293.520333</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>24528.653</t>
+          <t>-98891401.6326697</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>23154.66</t>
+          <t>144706547.925726</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>23500.08</t>
+          <t>135996230.660803</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>18121.984</t>
+          <t>-272816009.469385</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>18063.239</t>
+          <t>-166042432.926876</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>18184.318</t>
+          <t>-460193193.012453</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>18897.0928104522</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>22465.8299057477</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>25427.3588621016</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>31981.3733780814</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>42141.3632087978</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>51949.3977330489</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>63857.7099416562</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>83785.74135927</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>107463.143482498</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>86703.5918486847</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>91889.159169432</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>99225.5821698216</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>84392.1025843656</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>94666.2272461791</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>96420.5331169564</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>16448.757</t>
+          <t>0.0490490977774126</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16348.987</t>
+          <t>0.0404122030278802</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13859.222</t>
+          <t>0.0513600658579701</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>14287.132</t>
+          <t>0.06164417205954</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>13589.929</t>
+          <t>0.0730749163487949</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13485.095</t>
+          <t>0.0639887161943694</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>13148.076</t>
+          <t>0.0748685261657145</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>13207.201</t>
+          <t>0.0860300777081583</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>13036.412</t>
+          <t>0.0816111620289233</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>12525.338</t>
+          <t>0.0771975745204149</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>12588.832</t>
+          <t>0.0650031175106753</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>12579.835</t>
+          <t>0.0578279458245349</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>9471.056</t>
+          <t>0.056290817037713</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>9361.915</t>
+          <t>0.0606340930105056</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>9368.349</t>
+          <t>0.0599827735619074</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>14776.9214008654</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>16739.9524215496</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>18196.0280096259</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>22193.7519110302</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>27954.0870827977</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>38824.5658489559</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>47076.9438653062</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>63209.5582493684</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>82226.1345725627</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>63485.6725745478</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>59732.6189855976</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>60900.7731633253</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>56247.3780048832</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>60804.2311549813</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>66863.9578439625</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7162.892</t>
+          <t>16853.6987306169</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7144.284</t>
+          <t>19176.0605332431</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5638.239</t>
+          <t>20560.3177218463</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5804.915</t>
+          <t>25168.2823046459</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5264.464</t>
+          <t>31729.0055545692</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>6006.876</t>
+          <t>43991.8918801262</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>6063.294</t>
+          <t>53111.9352728305</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>6156.993</t>
+          <t>69054.2055802199</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>6405.77</t>
+          <t>90113.6364353751</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>5781.094</t>
+          <t>70023.0410691147</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>5339.744</t>
+          <t>70251.8877853129</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>4887.364</t>
+          <t>73536.0799716865</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>3600.267</t>
+          <t>65472.0671868118</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>3409.842</t>
+          <t>70967.1518031497</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3710.85</t>
+          <t>76752.4538062128</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>128284.008829398</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>139477.559335078</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>153537.51117354</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>99.05</t>
+          <t>189262.08899412</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>137.03</t>
+          <t>226913.435796682</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>99.61</t>
+          <t>291158.774454879</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>103.89</t>
+          <t>341341.290727237</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>462092.457192344</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>96.81</t>
+          <t>551072.318318459</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>108.33</t>
+          <t>484330.370315251</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>114.6</t>
+          <t>510452.10001564</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>146.4</t>
+          <t>586432.05711185</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>210.85</t>
+          <t>560965.936714791</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>227.18</t>
+          <t>607485.269119921</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>214.97</t>
+          <t>616337.951745181</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>15.088</t>
+          <t>84754.5462982644</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>90658.2053378873</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.154</t>
+          <t>88606.2596090317</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>8.682</t>
+          <t>87184.1911602689</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6.595</t>
+          <t>91392.8613884207</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5.387</t>
+          <t>100870.744584352</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.283</t>
+          <t>103655.413263283</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.336</t>
+          <t>103057.169519453</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.678</t>
+          <t>115590.538069635</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.964</t>
+          <t>104702.885992106</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2.664</t>
+          <t>103866.323821119</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>2.436</t>
+          <t>105573.561442369</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2.319</t>
+          <t>103243.779180337</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2.048</t>
+          <t>103637.812089136</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>108675.378112288</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>77220.6514556146</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>81997.4015362429</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>81129.0326485682</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>79489.3372104174</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>83491.5231813158</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>91340.0876331142</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>93799.2567596602</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>95194.6891889237</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>106248.830499079</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>95458.5876062098</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>88314.0365623108</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>88412.5065579276</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>89406.4107822127</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>88423.0048929225</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>92606.3207401523</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>17001.9963404511</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>17503.8024038047</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>21030.0702679475</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>28143.5506239071</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>36533.0759435552</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>44230.5864143392</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>56082.4864038023</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>82895.3290235153</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>96452.1450185365</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>81279.5034865876</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>79882.5509165231</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>89281.2795188027</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>85010.7867258014</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>97758.8134322801</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>99597.1390445767</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>11408567000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11290436000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>11921931000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>11554795000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>12478508000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>11990175000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>12362531000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>12500772000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>12607212000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1.2044e+10</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>11459093000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>12042350000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>11191338000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>11156219000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>11688135000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>20661817175.4686</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20587813032.999</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>18217554631.8914</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>18612148360.5748</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>18234077586.351</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17993604439.9295</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>17880909758.4704</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>18146449122.605</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>17925126035.0482</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>17592820564.6853</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>17407229096.2659</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>17693624259.7554</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>14453558936.3407</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>14325893689.5371</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>14814339315.0406</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>16448756792.1136</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>16348987104.7056</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13859221921.048</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>14287132324.8236</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>13589929194.0882</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>13485095414.5193</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>13148076460.0079</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>13207201357.8372</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>13036411943.7992</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>12525337596.4115</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>12588831833.2764</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>12579835062.9024</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>9471056139.4012</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>9361914861.6483</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>9368349072.26997</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>10706500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10630300</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9568400</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9569100</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9410900</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9266100</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>9319500</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>9366100</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>9348800</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>9185600</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>9134200</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>9073000</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>8627800</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>8569300</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>8803900</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>5846400</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5771600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6134400</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>5900100</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6407600</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6161600</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>6403900</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>6437000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6501100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6244700</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>6012300</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>6132800</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>5895000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>5897400</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>6170700</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>20661817175.4686</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>20587813032.999</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>18217554631.8914</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>18612148360.5748</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>18234077586.351</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>17993604439.9295</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17880909758.4704</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>18146449122.605</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>17925126035.0482</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>17592820564.6853</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>17407229096.2659</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>17693624259.7554</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>14453558936.3407</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>14325893689.5371</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>14814339315.0406</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11408567000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11290436000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11921931000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>11554795000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>12478508000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>11990175000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>12362531000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>12500772000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>12607212000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1.2044e+10</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>11459093000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>12042350000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>11191338000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>11156219000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>11688135000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>72755.1894132827</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>78810.8917631496</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>89408.4041190576</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>115064.161426121</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>148625.144013846</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>188250.323238368</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>233670.407930931</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>318100.594525816</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>392981.918667009</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>319526.976473395</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>327039.628131043</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>371363.491541286</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>351813.226932782</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>385683.095773541</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>398280.094568145</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>33855.9282132827</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>36679.8974431496</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>41590.3577190576</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>53311.9534261215</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>68261.9893938463</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>88222.4438583678</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>109194.49297093</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>151949.534575816</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>186565.581347009</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>151302.380153395</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>150134.375601043</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>162817.392341286</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>150482.882772782</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>168725.875063541</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>176349.652656092</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>492687.348242186</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>541488.433766703</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>549399.960888491</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>562077.058546181</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>579520.723204198</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>611366.858927374</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>638013.167850379</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>670542.113758235</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>706677.240201178</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>711895.885841194</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>754699.07636471</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>805939.429739054</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>828832.930353624</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>848290.709745186</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>857392.630489796</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
